--- a/FIP_Asymmetry_Workbook.xlsx
+++ b/FIP_Asymmetry_Workbook.xlsx
@@ -33,8 +33,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.0;(#,##0.0);&quot;–&quot;"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00;(#,##0.00);&quot;–&quot;"/>
+    <numFmt numFmtId="164" formatCode="#,##0.0;(#,##0.0);0.0"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00;(#,##0.00);0.00"/>
   </numFmts>
   <fonts count="6">
     <font>
